--- a/InputData/elec/MPCbS/Max Potential Capacity by Source.xlsx
+++ b/InputData/elec/MPCbS/Max Potential Capacity by Source.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mary Francis Swint\Vensim\eps-indonesia\InputData\elec\MPCbS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE6FE67B-CCEF-43C1-A1A0-9EDC914D92CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01ACCA2D-7449-4E48-AC5F-5047753FB801}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-5880" windowWidth="38640" windowHeight="21120" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -31362,8 +31362,7 @@
         <v>31</v>
       </c>
       <c r="B14" s="12">
-        <f>B2</f>
-        <v>9000000000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="14.5" x14ac:dyDescent="0.35">
@@ -32448,12 +32447,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -32601,15 +32597,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ECB6F87F-59CA-4CD9-AE08-9C2A2829C4A5}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BEEB8CD4-92FC-4564-B5B4-DA0F99881382}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -32633,10 +32633,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BEEB8CD4-92FC-4564-B5B4-DA0F99881382}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ECB6F87F-59CA-4CD9-AE08-9C2A2829C4A5}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>